--- a/data/trans_camb/P1410-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1410-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 1,1</t>
+          <t>-5,08; 1,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 1,11</t>
+          <t>-5,2; 1,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 2,62</t>
+          <t>-3,8; 2,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,71</t>
+          <t>-0,11; 6,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 5,44</t>
+          <t>-0,5; 5,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,17</t>
+          <t>-0,92; 3,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,66</t>
+          <t>-1,94; 2,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,31</t>
+          <t>-2,11; 2,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,61</t>
+          <t>-1,53; 2,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-10,75%</t>
+          <t>-1,35%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>113,12%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-74,16; 36,09</t>
+          <t>-74,78; 65,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 47,32</t>
+          <t>-76,18; 54,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,49; 83,88</t>
+          <t>-52,52; 85,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 950,48</t>
+          <t>-22,11; 1075,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 1005,66</t>
+          <t>-41,94; 738,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,68; 715,91</t>
+          <t>-46,08; 612,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 111,07</t>
+          <t>-44,17; 104,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 97,04</t>
+          <t>-50,87; 92,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 118,23</t>
+          <t>-31,65; 101,28</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,43</t>
+          <t>-1,4</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,09</t>
+          <t>-1,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,1; -0,17</t>
+          <t>-5,95; -0,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 0,6</t>
+          <t>-4,93; 0,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 2,13</t>
+          <t>-4,03; 2,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 1,53</t>
+          <t>-4,38; 1,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 2,02</t>
+          <t>-3,56; 2,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 1,06</t>
+          <t>-3,96; 1,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,22; -0,25</t>
+          <t>-4,34; -0,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,56</t>
+          <t>-3,43; 0,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,83</t>
+          <t>-3,01; 0,81</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-12,1%</t>
+          <t>-13,04%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-25,06%</t>
+          <t>-24,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,25%</t>
+          <t>-18,64%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-75,58; -1,91</t>
+          <t>-73,23; -6,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,53; 14,69</t>
+          <t>-63,59; 11,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 45,97</t>
+          <t>-49,31; 53,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,04; 49,52</t>
+          <t>-59,26; 33,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,88; 51,52</t>
+          <t>-50,71; 51,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,61; 27,61</t>
+          <t>-53,09; 28,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,22; -4,4</t>
+          <t>-60,79; -5,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 13,2</t>
+          <t>-49,57; 13,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-43,86; 17,98</t>
+          <t>-43,5; 14,41</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,78</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 4,43</t>
+          <t>-2,17; 4,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 4,56</t>
+          <t>-2,21; 4,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 5,45</t>
+          <t>-1,18; 5,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 5,87</t>
+          <t>-1,09; 5,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,09</t>
+          <t>-4,17; 1,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,33</t>
+          <t>0,0; 5,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 4,01</t>
+          <t>-0,76; 3,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,97</t>
+          <t>-2,16; 2,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,38</t>
+          <t>0,31; 4,48</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 172,06</t>
+          <t>-43,98; 167,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 188,43</t>
+          <t>-41,43; 151,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 206,16</t>
+          <t>-22,49; 213,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 252,56</t>
+          <t>-24,98; 262,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,84; 100,77</t>
+          <t>-79,87; 70,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 224,7</t>
+          <t>-5,46; 272,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 133,98</t>
+          <t>-17,52; 145,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 73,99</t>
+          <t>-44,1; 76,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 157,81</t>
+          <t>4,9; 159,99</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,47</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>2,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 5,77</t>
+          <t>-0,08; 5,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,51</t>
+          <t>-2,12; 3,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 6,05</t>
+          <t>-0,32; 5,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 5,29</t>
+          <t>0,13; 5,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 11,05</t>
+          <t>3,63; 10,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,66</t>
+          <t>-0,25; 4,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,7</t>
+          <t>0,68; 4,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,25</t>
+          <t>1,81; 6,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,89</t>
+          <t>0,48; 4,25</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 291,34</t>
+          <t>-4,37; 285,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 183,69</t>
+          <t>-48,8; 163,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 300,15</t>
+          <t>-11,96; 230,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 414,62</t>
+          <t>-9,38; 490,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>68,53; 833,44</t>
+          <t>96,99; 930,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,74; 304,08</t>
+          <t>-13,17; 339,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,7; 255,32</t>
+          <t>15,96; 242,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>40,66; 326,28</t>
+          <t>45,9; 310,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 202,3</t>
+          <t>6,54; 214,19</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-1,77</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-1,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 1,91</t>
+          <t>-5,77; 2,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 0,61</t>
+          <t>-6,49; 0,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 1,55</t>
+          <t>-5,38; 1,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 5,89</t>
+          <t>-2,57; 5,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 1,31</t>
+          <t>-5,07; 1,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,99</t>
+          <t>-4,53; 2,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,89</t>
+          <t>-2,81; 2,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,97; -0,18</t>
+          <t>-4,94; -0,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,1</t>
+          <t>-3,55; 0,99</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-33,35%</t>
+          <t>-35,28%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-11,55%</t>
+          <t>-11,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-24,06%</t>
+          <t>-25,15%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-83,02; 71,96</t>
+          <t>-78,88; 82,9</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-87,09; 42,33</t>
+          <t>-87,32; 51,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,65; 65,66</t>
+          <t>-71,43; 53,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,49; 318,98</t>
+          <t>-49,51; 313,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-90,99; 133,89</t>
+          <t>-90,03; 145,52</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-68,4; 116,3</t>
+          <t>-68,39; 116,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 107,94</t>
+          <t>-50,73; 91,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-81,98; 2,67</t>
+          <t>-81,72; 11,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,43; 36,48</t>
+          <t>-58,53; 39,16</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,81</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>3,55</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,7</t>
+          <t>-3,61; 3,76</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 0,24</t>
+          <t>-5,61; 0,79</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 6,53</t>
+          <t>-1,13; 6,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,89</t>
+          <t>1,07; 8,54</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,58; 6,94</t>
+          <t>0,33; 7,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,05</t>
+          <t>1,66; 7,0</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,02</t>
+          <t>0,13; 5,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,86</t>
+          <t>-1,87; 3,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,04</t>
+          <t>1,36; 5,79</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>224,47%</t>
+          <t>220,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>106,67%</t>
+          <t>102,83%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-52,22; 124,4</t>
+          <t>-54,56; 126,82</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-83,71; 24,71</t>
+          <t>-83,14; 34,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 196,1</t>
+          <t>-19,6; 204,75</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21,66; 1092,53</t>
+          <t>3,1; 841,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 743,33</t>
+          <t>-14,2; 759,61</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,51; 832,89</t>
+          <t>27,82; 824,29</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 207,37</t>
+          <t>-0,96; 214,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 117,32</t>
+          <t>-42,63; 127,93</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>25,19; 271,35</t>
+          <t>21,53; 250,88</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,28</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>2,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,36</t>
+          <t>-0,89; 3,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,99</t>
+          <t>-1,89; 2,06</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,93; 6,46</t>
+          <t>0,82; 5,52</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,64</t>
+          <t>-3,41; 0,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,05</t>
+          <t>-2,44; 2,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,89</t>
+          <t>-0,81; 3,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,34</t>
+          <t>-1,57; 1,38</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,72</t>
+          <t>-1,55; 1,48</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,15</t>
+          <t>0,57; 3,74</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-6,85%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>59,25%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 142,66</t>
+          <t>-24,87; 130,87</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 88,34</t>
+          <t>-44,98; 91,2</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11,59; 252,34</t>
+          <t>17,48; 219,94</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-65,36; 23,58</t>
+          <t>-65,14; 19,2</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 66,2</t>
+          <t>-47,22; 75,19</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 55,54</t>
+          <t>-15,68; 99,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 46,6</t>
+          <t>-35,07; 44,25</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 60,05</t>
+          <t>-35,28; 49,53</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 102,69</t>
+          <t>12,16; 125,28</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,42</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-1,24</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-4,75; -0,92</t>
+          <t>-4,62; -0,91</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 1,47</t>
+          <t>-2,61; 1,53</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 0,13</t>
+          <t>-3,1; 0,85</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,92</t>
+          <t>-3,1; 0,83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,45</t>
+          <t>-2,45; 1,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,32</t>
+          <t>-3,17; 0,26</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,62</t>
+          <t>-3,31; -0,61</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,93</t>
+          <t>-1,87; 0,99</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,51; -0,35</t>
+          <t>-2,6; -0,02</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-37,81%</t>
+          <t>-19,91%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-32,92%</t>
+          <t>-34,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-35,09%</t>
+          <t>-26,52%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-75,18; -20,79</t>
+          <t>-73,91; -19,48</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 39,64</t>
+          <t>-43,49; 42,33</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-75,78; 3,36</t>
+          <t>-50,33; 22,6</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-56,04; 32,38</t>
+          <t>-58,22; 25,51</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-46,74; 49,95</t>
+          <t>-46,66; 60,71</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-58,74; 12,39</t>
+          <t>-56,72; 9,91</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-58,67; -13,6</t>
+          <t>-60,1; -14,16</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-36,48; 23,26</t>
+          <t>-35,03; 26,71</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-62,99; -10,69</t>
+          <t>-46,08; 1,3</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,72</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,22</t>
+          <t>-1,7; 0,23</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,05</t>
+          <t>-1,76; 0,12</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,6</t>
+          <t>-0,22; 1,77</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,36</t>
+          <t>-0,6; 1,26</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,86</t>
+          <t>-0,32; 1,74</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,17</t>
+          <t>-0,25; 1,44</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,58</t>
+          <t>-0,84; 0,54</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,63</t>
+          <t>-0,7; 0,65</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,13</t>
+          <t>0,03; 1,36</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-32,75; 5,29</t>
+          <t>-34,05; 5,66</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 1,3</t>
+          <t>-34,56; 2,84</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 37,82</t>
+          <t>-4,27; 43,37</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 42,19</t>
+          <t>-13,34; 37,13</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 56,14</t>
+          <t>-7,43; 54,29</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 34,53</t>
+          <t>-5,85; 44,97</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 15,17</t>
+          <t>-18,95; 14,03</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 16,44</t>
+          <t>-15,57; 16,71</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 29,43</t>
+          <t>0,57; 36,01</t>
         </is>
       </c>
     </row>
